--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260819.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260819.xlsx
@@ -865,17 +865,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>2,043,288</t>
+          <t>5,407,520</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -887,17 +887,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>5,407,520</t>
+          <t>2,043,288</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>875,349</t>
+          <t>102,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>102,000</t>
+          <t>875,349</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>590,000</t>
+          <t>140,921</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>140,921</t>
+          <t>590,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>202609WTEU6F</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>電子指數期貨</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,044,587</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>202609WTEU6F</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>電子指數期貨</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>2,044,587</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>10,821,121</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>7,318,249</t>
+          <t>2,651,703</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>1,407,384</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>1,407,384</t>
+          <t>10,821,121</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>2,651,703</t>
+          <t>7,318,249</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>1,210,076</t>
+          <t>95,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>821,000</t>
+          <t>1,210,076</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>95,000</t>
+          <t>821,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>185,000</t>
+          <t>296,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>508,000</t>
+          <t>185,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>5,063,956</t>
+          <t>792,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>792,000</t>
+          <t>232,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>296,000</t>
+          <t>508,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>232,000</t>
+          <t>5,063,956</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>1,024,121</t>
+          <t>117,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>1,794,000</t>
+          <t>1,024,121</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>117,000</t>
+          <t>1,794,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>160,000</t>
+          <t>66,538</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>338,000</t>
+          <t>160,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>66,538</t>
+          <t>338,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>174,000</t>
+          <t>694,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>182,000</t>
+          <t>174,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>259,000</t>
+          <t>182,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>694,000</t>
+          <t>259,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
